--- a/scrutiny/public/samples/ingestion/00 READ ME - Format guide.xlsx
+++ b/scrutiny/public/samples/ingestion/00 READ ME - Format guide.xlsx
@@ -10757,7 +10757,7 @@
         <v>Text</v>
       </c>
       <c r="F4" s="1" t="str">
-        <v>SYN-PUNE-01</v>
+        <v>PUNE-WARD-01</v>
       </c>
       <c r="G4" s="1" t="str">
         <v>Ward / range / circle code the taxpayer belongs to</v>

--- a/scrutiny/public/samples/ingestion/00 READ ME - Format guide.xlsx
+++ b/scrutiny/public/samples/ingestion/00 READ ME - Format guide.xlsx
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -579,19 +579,19 @@
         <v>7</v>
       </c>
       <c r="B12" s="1" t="str">
-        <v>Reply letter</v>
+        <v>Due-date extensions</v>
       </c>
       <c r="C12" s="1" t="str">
-        <v>One per taxpayer reply</v>
+        <v>One file, updated when an extension is notified</v>
       </c>
       <c r="D12" s="1" t="str">
-        <v>3 Reply letters/EIU-SAMPLE-0001 reply.pdf</v>
+        <v>2 Registers/extensions.xlsx</v>
       </c>
       <c r="E12" s="1" t="str">
-        <v>EIU signals &gt; open the signal &gt; Record reply &gt; attach</v>
+        <v>Data sources &gt; Registers &gt; Due-date extensions</v>
       </c>
       <c r="F12" s="1" t="str">
-        <v>Optional: free-form PDF, Word (.docx) or text</v>
+        <v>When a GSTR-3B due date is extended; otherwise the statutory dates apply</v>
       </c>
     </row>
     <row r="13">
@@ -599,87 +599,107 @@
         <v>8</v>
       </c>
       <c r="B13" s="1" t="str">
+        <v>Reply letter</v>
+      </c>
+      <c r="C13" s="1" t="str">
+        <v>One per taxpayer reply</v>
+      </c>
+      <c r="D13" s="1" t="str">
+        <v>3 Reply letters/EIU-SAMPLE-0001 reply.pdf</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <v>EIU signals &gt; open the signal &gt; Record reply &gt; attach</v>
+      </c>
+      <c r="F13" s="1" t="str">
+        <v>Optional: free-form PDF, Word (.docx) or text</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>9</v>
+      </c>
+      <c r="B14" s="1" t="str">
         <v>Rule matrix</v>
       </c>
-      <c r="C13" s="1" t="str">
+      <c r="C14" s="1" t="str">
         <v>One, set up once</v>
       </c>
-      <c r="D13" s="1" t="str">
+      <c r="D14" s="1" t="str">
         <v>(not included: already on the platform)</v>
       </c>
-      <c r="E13" s="1" t="str">
+      <c r="E14" s="1" t="str">
         <v>Placed in the data folder by the administrator</v>
       </c>
-      <c r="F13" s="1" t="str">
+      <c r="F14" s="1" t="str">
         <v>Already in place</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="str">
-        <v>How to read this guide</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="str">
-        <v>Sheet</v>
-      </c>
-      <c r="B16" s="1" t="str">
-        <v>What it covers</v>
+        <v>How to read this guide</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="str">
-        <v>Returns - sheets</v>
+        <v>Sheet</v>
       </c>
       <c r="B17" s="1" t="str">
-        <v>Every sheet of the returns workbook: what it holds and whether the platform reads it</v>
+        <v>What it covers</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="str">
-        <v>Returns - columns</v>
+        <v>Returns - sheets</v>
       </c>
       <c r="B18" s="1" t="str">
-        <v>Every column of every returns sheet, exactly as spelled in the export, and whether the platform reads it</v>
+        <v>Every sheet of the returns workbook: what it holds and whether the platform reads it</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="str">
-        <v>Registers - columns</v>
+        <v>Returns - columns</v>
       </c>
       <c r="B19" s="1" t="str">
-        <v>Every column of the five registers: required or not, the accepted format, an example and the meaning</v>
+        <v>Every column of every returns sheet, exactly as spelled in the export, and whether the platform reads it</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="str">
-        <v>Rules</v>
+        <v>Registers - columns</v>
       </c>
       <c r="B20" s="1" t="str">
-        <v>The rules a file must follow to be accepted. A pipeline should check these before delivering a file</v>
+        <v>Every column of the six registers: required or not, the accepted format, an example and the meaning</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="str">
+        <v>Rules</v>
+      </c>
+      <c r="B21" s="1" t="str">
+        <v>The rules a file must follow to be accepted. A pipeline should check these before delivering a file</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="str">
         <v>Other sources</v>
       </c>
-      <c r="B21" s="1" t="str">
+      <c r="B22" s="1" t="str">
         <v>Data the rule matrix needs that no current file provides (for planning, not required now)</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="str">
-        <v>Note on the returns workbook</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="str">
+        <v>Note on the returns workbook</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="str">
         <v>The banner of the real workbooks links to microvistatech.com, so these files appear to be exported by a GST software tool, not downloaded directly from the GST portal. Confirm the source before automating it.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F25"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -10660,7 +10680,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G60"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -11913,9 +11933,147 @@
         <v>Free text</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="1" t="str">
+        <v>Due-date extensions</v>
+      </c>
+      <c r="B55" s="1" t="str">
+        <v>extensions.xlsx</v>
+      </c>
+      <c r="C55" s="1" t="str">
+        <v>fy</v>
+      </c>
+      <c r="D55" s="1" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="E55" s="1" t="str">
+        <v>Financial year like 2025-26</v>
+      </c>
+      <c r="F55" s="1" t="str">
+        <v>2025-26</v>
+      </c>
+      <c r="G55" s="1" t="str">
+        <v>Financial year of the tax period</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="str">
+        <v>Due-date extensions</v>
+      </c>
+      <c r="B56" s="1" t="str">
+        <v>extensions.xlsx</v>
+      </c>
+      <c r="C56" s="1" t="str">
+        <v>month</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="E56" s="1" t="str">
+        <v>Month (Apr to Mar)</v>
+      </c>
+      <c r="F56" s="1" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="G56" s="1" t="str">
+        <v>Last month of the tax period (for QRMP filers, the last month of the quarter)</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="str">
+        <v>Due-date extensions</v>
+      </c>
+      <c r="B57" s="1" t="str">
+        <v>extensions.xlsx</v>
+      </c>
+      <c r="C57" s="1" t="str">
+        <v>filing</v>
+      </c>
+      <c r="D57" s="1" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="E57" s="1" t="str">
+        <v>One of: All, Monthly, QRMP</v>
+      </c>
+      <c r="F57" s="1" t="str">
+        <v>All</v>
+      </c>
+      <c r="G57" s="1" t="str">
+        <v>Which filers the extension covers: All, Monthly or QRMP</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="str">
+        <v>Due-date extensions</v>
+      </c>
+      <c r="B58" s="1" t="str">
+        <v>extensions.xlsx</v>
+      </c>
+      <c r="C58" s="1" t="str">
+        <v>states</v>
+      </c>
+      <c r="D58" s="1" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="E58" s="1" t="str">
+        <v>"All" or State codes such as 27, 24</v>
+      </c>
+      <c r="F58" s="1" t="str">
+        <v>All</v>
+      </c>
+      <c r="G58" s="1" t="str">
+        <v>"All", or the State codes covered, separated by commas (e.g. 27, 24)</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="str">
+        <v>Due-date extensions</v>
+      </c>
+      <c r="B59" s="1" t="str">
+        <v>extensions.xlsx</v>
+      </c>
+      <c r="C59" s="1" t="str">
+        <v>due_date</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="E59" s="1" t="str">
+        <v>Date (DD-MM-YYYY or YYYY-MM-DD)</v>
+      </c>
+      <c r="F59" s="1" t="str">
+        <v>22-01-2026</v>
+      </c>
+      <c r="G59" s="1" t="str">
+        <v>The extended due date</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="str">
+        <v>Due-date extensions</v>
+      </c>
+      <c r="B60" s="1" t="str">
+        <v>extensions.xlsx</v>
+      </c>
+      <c r="C60" s="1" t="str">
+        <v>notification</v>
+      </c>
+      <c r="D60" s="1" t="str">
+        <v>No</v>
+      </c>
+      <c r="E60" s="1" t="str">
+        <v>Text</v>
+      </c>
+      <c r="F60" s="1" t="str">
+        <v>Notification No. 01/2026-Central Tax</v>
+      </c>
+      <c r="G60" s="1" t="str">
+        <v>Notification that extended it</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G60"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12134,10 +12292,10 @@
         <v>Registers</v>
       </c>
       <c r="C15" s="1" t="str">
-        <v>Each upload replaces the previous version of that register completely (the previous version and the original file are kept). Send the full register every time, not only changes.</v>
+        <v>Each upload adds to the register: new rows are added, a row with the same key (GSTIN, signal_id, demand_id ...) is updated, and every row already saved stays. Send only new or changed rows if you like. The previous version and the original file are kept.</v>
       </c>
       <c r="D15" s="1" t="str">
-        <v>Rows missing from a new upload disappear from the platform.</v>
+        <v>A row cannot be removed by leaving it out of a new upload.</v>
       </c>
     </row>
     <row r="16">
